--- a/Copy of AI Audit Log_NguyenTienLoc_DE190986.xlsx
+++ b/Copy of AI Audit Log_NguyenTienLoc_DE190986.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="19392" windowHeight="11472" activeTab="1"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="19392" windowHeight="11472" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
-    <sheet name="Assignment 1" sheetId="2" r:id="rId2"/>
-    <sheet name="Assignment 2" sheetId="3" r:id="rId3"/>
-    <sheet name="Assignment 3" sheetId="4" r:id="rId4"/>
+    <sheet name="Week1" sheetId="2" r:id="rId2"/>
+    <sheet name="Week2" sheetId="3" r:id="rId3"/>
+    <sheet name="Week3" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="55">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -138,13 +138,85 @@
   </si>
   <si>
     <t>“Phản hồi: AI đưa ví dụ về hệ thống quản lý sinh viên với các bước từ khảo sát yêu cầu đến bảo trì hệ thống. Kiểm chứng: Tôi nhận thấy AI chưa đề cập đến kiểm thử bảo mật và phân quyền người dùng. Tôi đã tự bổ sung thêm để ví dụ sát với thực tế hơn.”</t>
+  </si>
+  <si>
+    <t>“Use Case Diagram là gì? Hãy giải thích khái niệm Use Case Diagram trong phân tích và thiết kế phần mềm.”</t>
+  </si>
+  <si>
+    <t>“Phản hồi: AI giải thích Use Case Diagram là sơ đồ mô tả sự tương tác giữa người dùng (actor) và hệ thống thông qua các chức năng chính. AI cũng nêu vai trò của sơ đồ trong việc phân tích yêu cầu hệ thống. Quyết định: Tôi chỉ giữ lại các ý liên quan đến actor, use case và mối quan hệ với hệ thống để phù hợp nội dung môn học.”</t>
+  </si>
+  <si>
+    <t>“Hãy nêu các thành phần chính của Use Case Diagram.”</t>
+  </si>
+  <si>
+    <t>“Phản hồi: AI trình bày các thành phần gồm Actor, Use Case, System Boundary và các mối quan hệ như Include, Extend, Association. AI còn đưa thêm ví dụ minh họa về hệ thống quản lý thư viện. Quyết định: Tôi chọn các thành phần cơ bản và ví dụ đơn giản để dễ áp dụng vào bài tập.”</t>
+  </si>
+  <si>
+    <t>“Mô tả quy trình xây dựng Use Case Diagram và các bước thực hiện.”</t>
+  </si>
+  <si>
+    <t>“Phản hồi: AI liệt kê các bước gồm: xác định yêu cầu hệ thống, xác định actor, xác định use case, vẽ mối quan hệ và kiểm tra tính đầy đủ của sơ đồ. Kiểm chứng: Tôi nhận thấy AI chưa nhấn mạnh việc phân tích yêu cầu người dùng trước khi vẽ sơ đồ nên tôi bổ sung bước khảo sát thực tế.”</t>
+  </si>
+  <si>
+    <t>“So sánh Include và Extend trong Use Case Diagram. Khi nào nên sử dụng mỗi loại?”</t>
+  </si>
+  <si>
+    <t>“Phản hồi: AI giải thích Include dùng cho chức năng bắt buộc và tái sử dụng, còn Extend dùng cho chức năng mở rộng hoặc điều kiện đặc biệt. Kiểm chứng: Tôi nhận thấy AI chưa đưa ví dụ thực tế rõ ràng nên tôi bổ sung ví dụ ‘Đăng nhập’ là Include và ‘Quên mật khẩu’ là Extend.”</t>
+  </si>
+  <si>
+    <t>“Liệt kê các bước phân tích yêu cầu để xây dựng Use Case Diagram cho hệ thống quản lý sinh viên.”</t>
+  </si>
+  <si>
+    <t>“Phản hồi: AI liệt kê các bước gồm: xác định tác nhân, xác định chức năng quản lý sinh viên, đăng ký môn học, xem điểm và quản lý tài khoản. Quyết định: Tôi giữ nguyên các chức năng chính nhưng viết lại ngắn gọn hơn để phù hợp báo cáo.”</t>
+  </si>
+  <si>
+    <t>“Hãy cho ví dụ thực tế về Use Case Diagram trong hệ thống quản lý trường học.”</t>
+  </si>
+  <si>
+    <t>“Phản hồi: AI đưa ví dụ gồm các actor như Sinh viên, Giảng viên, Quản trị viên và các use case như đăng nhập, đăng ký môn học, nhập điểm, xem thời khóa biểu. Kiểm chứng: Tôi nhận thấy AI chưa đề cập rõ quyền hạn của từng actor nên tôi bổ sung thêm phân quyền để ví dụ sát với thực tế hơn.”</t>
+  </si>
+  <si>
+    <t>"Class Diagram cho hệ thống car rental là gì? Hãy xác định các thành phần chính cần có trong sơ đồ: users, vehicles, bookings và payments."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI xác định các lớp cơ bản gồm User, Car, Booking và Payment cùng các thuộc tính cần thiết cho mỗi lớp. Quyết định: Tôi giữ lại cấu trúc lớp cơ bản và xác định rõ User cần được abstract thành Customer và Staff để phù hợp với yêu cầu hệ thống.</t>
+  </si>
+  <si>
+    <t>"Hãy nêu các yêu cầu thiết kế cho Class Diagram của hệ thống car rental: Customer và Staff kế thừa từ User, Customer tạo nhiều Booking, Booking liên kết 1 Car, Booking có 1 hoặc nhiều Payment."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI trình bày đầy đủ các yêu cầu với quan hệ Inheritance, Association và Composition. AI nhận ra pattern Repository để tách business logic khỏi data access. Quyết định: Tôi chọn áp dụng Repository Pattern và xác định rõ các quan hệ UML cần dùng trong sơ đồ.</t>
+  </si>
+  <si>
+    <t>"Mô tả quy trình vẽ Class Diagram cho hệ thống car rental theo đúng chuẩn UML: kế thừa và implement interface, Association/Aggregation/Composition, Dependency giữa Service và Repository, Multiplicity rõ ràng."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI hướng dẫn các bước: xác định class hierarchy, vẽ quan hệ kế thừa, thêm interface IGenericRepository&lt;T&gt;, vẽ dependency từ PaymentService đến các Repository. Kiểm chứng: Tôi nhận thấy cần vẽ filled diamond (◆) cho Composition Booking→Payment và hollow triangle cho Inheritance.</t>
+  </si>
+  <si>
+    <t>"Xem xét và đánh giá bản Class Diagram tôi đã vẽ. Chỉ ra các lỗi sai về multiplicity của Booking→Car, quan hệ Composition, Repository Pattern và các lỗi UML khác."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI phát hiện 4 lỗi chính: (1) IGenericRepository bị vẽ 2 lần – thừa; (2) BookingRepository và PaymentRepository không implement đúng IGenericRepository&lt;T&gt;; (3) Multiplicity Booking→Car sai (0..* thay vì 1); (4) Composition Booking→Payment chưa dùng filled diamond. Kiểm chứng: Tôi đối chiếu lại sơ đồ và xác nhận toàn bộ 4 lỗi đều đúng, cần sửa lại.</t>
+  </si>
+  <si>
+    <t>"Liệt kê các bước sửa lại Class Diagram cho đúng chuẩn: xóa IGenericRepository thừa, sửa multiplicity Booking→Car thành 0..*—1, vẽ Composition (◆) từ Booking sang Payment, BookingRepository và PaymentRepository implement IGenericRepository&lt;T&gt; bằng dashed + hollow triangle, PaymentService depend vào cả 2 Repository."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI xác nhận danh sách sửa đổi và bổ sung thêm: thêm methods đặc thù cho Repository (findByCustomer, findByStatus), thêm field paymentType cho Payment, bổ sung legend giải thích ký hiệu mũi tên. Quyết định: Tôi áp dụng toàn bộ các chỉnh sửa và nhờ AI vẽ lại sơ đồ hoàn chỉnh.</t>
+  </si>
+  <si>
+    <t>"Bạn hãy vẽ lại cho tôi cái sơ đồ Class Diagram mới, đã sửa đầy đủ các lỗi đã phân tích: đúng Repository Pattern, đúng multiplicity, đúng Composition, đúng interface implementation."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI vẽ lại sơ đồ hoàn chỉnh với: User (abstract) → Customer + Staff (kế thừa đúng); Customer 1→0..* Booking; Booking 0..*→1 Car (association); Booking 1◆→1..* Payment (composition); IGenericRepository&lt;T&gt; được implement bởi BookingRepository và PaymentRepository; PaymentService depend vào 2 Repository bằng dashed arrow «uses». Kiểm chứng: Tôi đối chiếu với yêu cầu đề bài và xác nhận sơ đồ đã đáp ứng đầy đủ 5 tiêu chí: inheritance, interface implementation, association/composition, dependency, multiplicity.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,6 +231,19 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -197,7 +282,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -224,6 +309,13 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -761,18 +853,227 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="27.5" customWidth="1"/>
+    <col min="3" max="3" width="38.5" customWidth="1"/>
+    <col min="4" max="4" width="52.09765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="82.8">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="69">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="69">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="69">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="55.2">
+      <c r="A6" s="12">
+        <v>5</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="69">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="33.59765625" customWidth="1"/>
+    <col min="3" max="3" width="29.3984375" customWidth="1"/>
+    <col min="4" max="4" width="51.796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="74.400000000000006" customHeight="1">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="94.2" customHeight="1">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="102" customHeight="1">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="100.2" customHeight="1">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="167.4" customHeight="1">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="129" customHeight="1">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>